--- a/r4-core-131-Gemeindecode/StructureDefinition-at-core-valueset.xlsx
+++ b/r4-core-131-Gemeindecode/StructureDefinition-at-core-valueset.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-valueset</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-valueset</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-07T12:03:29+00:00</t>
+    <t>2026-09-11T12:27:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -359,7 +359,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -746,7 +746,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -935,7 +935,7 @@
     <t>systemOID</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-valueset-systemoid}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-valueset-systemoid}
 </t>
   </si>
   <si>
@@ -1081,7 +1081,7 @@
     <t>Details of how a designation would be used.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/designation-use</t>
+    <t>http://hl7.org/fhir/ValueSet/designation-use|4.0.1</t>
   </si>
   <si>
     <t>ValueSet.compose.include.concept.designation.value</t>
@@ -1156,7 +1156,7 @@
     <t>ValueSet.compose.include.valueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ValueSet)
+    <t xml:space="preserve">canonical(ValueSet|4.0.1)
 </t>
   </si>
   <si>
@@ -1751,7 +1751,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="83.78125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="71.125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
